--- a/isolated_excel/Table 4 - Paper vs Current.xlsx
+++ b/isolated_excel/Table 4 - Paper vs Current.xlsx
@@ -478,10 +478,10 @@
         <v>3.47</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3.519478260869567</v>
+        <v>3.499741379310346</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.04947826086956697</v>
+        <v>0.02974137931034626</v>
       </c>
     </row>
     <row r="3">
@@ -494,10 +494,10 @@
         <v>3.4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.448012329545969</v>
+        <v>3.42868537831944</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.04801232954596868</v>
+        <v>0.02868537831944051</v>
       </c>
     </row>
     <row r="4">
@@ -510,10 +510,10 @@
         <v>95.41</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>95.65217391304348</v>
+        <v>95.68965517241379</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.2421739130434872</v>
+        <v>0.279655172413797</v>
       </c>
     </row>
     <row r="5">
@@ -526,10 +526,10 @@
         <v>4.59</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4.347826086956522</v>
+        <v>4.310344827586207</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.2421739130434784</v>
+        <v>-0.2796551724137926</v>
       </c>
     </row>
     <row r="6">
@@ -542,10 +542,10 @@
         <v>3.68</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3.718909090909092</v>
+        <v>3.696486486486487</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.03890909090909211</v>
+        <v>0.0164864864864871</v>
       </c>
     </row>
     <row r="7">
@@ -574,10 +574,10 @@
         <v>4.06</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>3.983943837120484</v>
+        <v>3.972276416934467</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>-0.076056162879516</v>
+        <v>-0.0877235830655323</v>
       </c>
     </row>
     <row r="9">
@@ -590,10 +590,10 @@
         <v>0.86</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.8834156315349508</v>
+        <v>0.8810417533861374</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.02341563153495085</v>
+        <v>0.02104175338613745</v>
       </c>
     </row>
     <row r="10">
@@ -606,10 +606,10 @@
         <v>13.96</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>14.58478488287689</v>
+        <v>14.56591488300176</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.6247848828768845</v>
+        <v>0.6059148830017609</v>
       </c>
     </row>
     <row r="11">
@@ -622,10 +622,10 @@
         <v>88.28</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>94.25806451612905</v>
+        <v>94.54147465437789</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.978064516129052</v>
+        <v>6.261474654377892</v>
       </c>
     </row>
   </sheetData>
@@ -679,7 +679,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Jul 2026; 115 monthly observations</t>
+          <t>Jan 2017 to Aug 2026; 116 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Table 4 - Paper vs Current.xlsx
+++ b/isolated_excel/Table 4 - Paper vs Current.xlsx
@@ -443,7 +443,7 @@
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,10 +478,10 @@
         <v>3.47</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3.499741379310346</v>
+        <v>3.479145299145301</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.02974137931034626</v>
+        <v>0.009145299145300712</v>
       </c>
     </row>
     <row r="3">
@@ -494,10 +494,10 @@
         <v>3.4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.42868537831944</v>
+        <v>3.408469136214709</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.02868537831944051</v>
+        <v>0.008469136214709128</v>
       </c>
     </row>
     <row r="4">
@@ -510,10 +510,10 @@
         <v>95.41</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>95.68965517241379</v>
+        <v>95.72649572649573</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.279655172413797</v>
+        <v>0.3164957264957309</v>
       </c>
     </row>
     <row r="5">
@@ -526,10 +526,10 @@
         <v>4.59</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4.310344827586207</v>
+        <v>4.273504273504273</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.2796551724137926</v>
+        <v>-0.3164957264957264</v>
       </c>
     </row>
     <row r="6">
@@ -542,10 +542,10 @@
         <v>3.68</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3.696486486486487</v>
+        <v>3.673214285714287</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.0164864864864871</v>
+        <v>-0.006785714285713063</v>
       </c>
     </row>
     <row r="7">
@@ -574,10 +574,10 @@
         <v>4.06</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>3.972276416934467</v>
+        <v>3.961386811469624</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>-0.0877235830655323</v>
+        <v>-0.0986131885303756</v>
       </c>
     </row>
     <row r="9">
@@ -590,10 +590,10 @@
         <v>0.86</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.8810417533861374</v>
+        <v>0.8782644727023218</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.02104175338613745</v>
+        <v>0.01826447270232179</v>
       </c>
     </row>
     <row r="10">
@@ -606,10 +606,10 @@
         <v>13.96</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>14.56591488300176</v>
+        <v>14.54247474070697</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.6059148830017609</v>
+        <v>0.5824747407069726</v>
       </c>
     </row>
     <row r="11">
@@ -622,10 +622,10 @@
         <v>88.28</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>94.54147465437789</v>
+        <v>94.79262672811062</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6.261474654377892</v>
+        <v>6.512626728110618</v>
       </c>
     </row>
   </sheetData>
@@ -679,7 +679,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Aug 2026; 116 monthly observations</t>
+          <t>Jan 2017 to Sept 2026; 117 monthly observations</t>
         </is>
       </c>
     </row>
